--- a/test-data/成绩-测试数据.xlsx
+++ b/test-data/成绩-测试数据.xlsx
@@ -429,7 +429,7 @@
   <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -2150,7 +2150,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1. 第一列是学生姓名（与花名册一致），其余列为科目成绩。</t>
+          <t>1. 第一列是学生姓名（与示例花名册一致），其余列为科目成绩。</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4. 也支持首列为「学籍号」的格式；不认识的列会被忽略。</t>
+          <t>4. 若导入时提示“未匹配到任何学生成绩”，说明当前花名册姓名已改动，请改用「学籍号版」。</t>
         </is>
       </c>
     </row>
